--- a/src/width_txt/Максимальные_значения_фильтра_дробной_задержки_АЦП_№3.xlsx
+++ b/src/width_txt/Максимальные_значения_фильтра_дробной_задержки_АЦП_№3.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="608" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="912" uniqueCount="76">
   <si>
     <t>Row</t>
   </si>
@@ -310,10 +310,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="0">
-        <v>2048</v>
+        <v>1450</v>
       </c>
       <c r="C2" s="0">
-        <v>10239</v>
+        <v>7248</v>
       </c>
     </row>
     <row r="3">
@@ -321,10 +321,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="0">
-        <v>8192</v>
+        <v>5800</v>
       </c>
       <c r="C3" s="0">
-        <v>28668</v>
+        <v>20290</v>
       </c>
     </row>
     <row r="4">
@@ -332,10 +332,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="0">
-        <v>18432</v>
+        <v>13050</v>
       </c>
       <c r="C4" s="0">
-        <v>65301</v>
+        <v>46372</v>
       </c>
     </row>
     <row r="5">
@@ -343,10 +343,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="0">
-        <v>36864</v>
+        <v>26100</v>
       </c>
       <c r="C5" s="0">
-        <v>127341</v>
+        <v>91286</v>
       </c>
     </row>
     <row r="6">
@@ -354,10 +354,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="0">
-        <v>63488</v>
+        <v>44950</v>
       </c>
       <c r="C6" s="0">
-        <v>221192</v>
+        <v>160835</v>
       </c>
     </row>
     <row r="7">
@@ -365,10 +365,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="0">
-        <v>98304</v>
+        <v>69600</v>
       </c>
       <c r="C7" s="0">
-        <v>353460</v>
+        <v>262259</v>
       </c>
     </row>
     <row r="8">
@@ -376,10 +376,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="0">
-        <v>143360</v>
+        <v>101500</v>
       </c>
       <c r="C8" s="0">
-        <v>532853</v>
+        <v>405698</v>
       </c>
     </row>
     <row r="9">
@@ -387,10 +387,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="0">
-        <v>202752</v>
+        <v>143550</v>
       </c>
       <c r="C9" s="0">
-        <v>766082</v>
+        <v>601294</v>
       </c>
     </row>
     <row r="10">
@@ -398,10 +398,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="0">
-        <v>276480</v>
+        <v>195750</v>
       </c>
       <c r="C10" s="0">
-        <v>1075371</v>
+        <v>862084</v>
       </c>
     </row>
     <row r="11">
@@ -409,10 +409,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="0">
-        <v>368640</v>
+        <v>261000</v>
       </c>
       <c r="C11" s="0">
-        <v>1460498</v>
+        <v>1201106</v>
       </c>
     </row>
     <row r="12">
@@ -420,10 +420,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="0">
-        <v>479232</v>
+        <v>339300</v>
       </c>
       <c r="C12" s="0">
-        <v>1933642</v>
+        <v>1637191</v>
       </c>
     </row>
     <row r="13">
@@ -431,10 +431,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="0">
-        <v>616448</v>
+        <v>436450</v>
       </c>
       <c r="C13" s="0">
-        <v>2503082</v>
+        <v>2189171</v>
       </c>
     </row>
     <row r="14">
@@ -442,10 +442,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="0">
-        <v>780288</v>
+        <v>552450</v>
       </c>
       <c r="C14" s="0">
-        <v>3183012</v>
+        <v>2880222</v>
       </c>
     </row>
     <row r="15">
@@ -453,10 +453,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="0">
-        <v>976896</v>
+        <v>691650</v>
       </c>
       <c r="C15" s="0">
-        <v>3983102</v>
+        <v>3734972</v>
       </c>
     </row>
     <row r="16">
@@ -464,10 +464,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="0">
-        <v>1208320</v>
+        <v>855500</v>
       </c>
       <c r="C16" s="0">
-        <v>4918260</v>
+        <v>4783837</v>
       </c>
     </row>
     <row r="17">
@@ -475,10 +475,10 @@
         <v>16</v>
       </c>
       <c r="B17" s="0">
-        <v>1482752</v>
+        <v>1049800</v>
       </c>
       <c r="C17" s="0">
-        <v>6008683</v>
+        <v>6060136</v>
       </c>
     </row>
     <row r="18">
@@ -486,10 +486,10 @@
         <v>17</v>
       </c>
       <c r="B18" s="0">
-        <v>1804288</v>
+        <v>1277450</v>
       </c>
       <c r="C18" s="0">
-        <v>7275591</v>
+        <v>7601526</v>
       </c>
     </row>
     <row r="19">
@@ -497,10 +497,10 @@
         <v>18</v>
       </c>
       <c r="B19" s="0">
-        <v>2179072</v>
+        <v>1542800</v>
       </c>
       <c r="C19" s="0">
-        <v>8784611</v>
+        <v>9451468</v>
       </c>
     </row>
     <row r="20">
@@ -508,10 +508,10 @@
         <v>19</v>
       </c>
       <c r="B20" s="0">
-        <v>2615296</v>
+        <v>1851650</v>
       </c>
       <c r="C20" s="0">
-        <v>10524914</v>
+        <v>11659207</v>
       </c>
     </row>
     <row r="21">
@@ -519,10 +519,10 @@
         <v>20</v>
       </c>
       <c r="B21" s="0">
-        <v>3121152</v>
+        <v>2209800</v>
       </c>
       <c r="C21" s="0">
-        <v>12526874</v>
+        <v>14281237</v>
       </c>
     </row>
     <row r="22">
@@ -530,10 +530,10 @@
         <v>21</v>
       </c>
       <c r="B22" s="0">
-        <v>3706880</v>
+        <v>2624500</v>
       </c>
       <c r="C22" s="0">
-        <v>14829402</v>
+        <v>17384190</v>
       </c>
     </row>
     <row r="23">
@@ -541,10 +541,10 @@
         <v>22</v>
       </c>
       <c r="B23" s="0">
-        <v>4386816</v>
+        <v>3105900</v>
       </c>
       <c r="C23" s="0">
-        <v>17477704</v>
+        <v>21043391</v>
       </c>
     </row>
     <row r="24">
@@ -552,10 +552,10 @@
         <v>23</v>
       </c>
       <c r="B24" s="0">
-        <v>5173248</v>
+        <v>3662700</v>
       </c>
       <c r="C24" s="0">
-        <v>20530396</v>
+        <v>25351546</v>
       </c>
     </row>
     <row r="25">
@@ -563,10 +563,10 @@
         <v>24</v>
       </c>
       <c r="B25" s="0">
-        <v>6090752</v>
+        <v>4312300</v>
       </c>
       <c r="C25" s="0">
-        <v>24063381</v>
+        <v>30420198</v>
       </c>
     </row>
     <row r="26">
@@ -574,10 +574,10 @@
         <v>25</v>
       </c>
       <c r="B26" s="0">
-        <v>7165952</v>
+        <v>5073550</v>
       </c>
       <c r="C26" s="0">
-        <v>28174785</v>
+        <v>36388416</v>
       </c>
     </row>
     <row r="27">
@@ -585,10 +585,10 @@
         <v>26</v>
       </c>
       <c r="B27" s="0">
-        <v>8437760</v>
+        <v>5974000</v>
       </c>
       <c r="C27" s="0">
-        <v>32997307</v>
+        <v>43431489</v>
       </c>
     </row>
     <row r="28">
@@ -596,10 +596,10 @@
         <v>27</v>
       </c>
       <c r="B28" s="0">
-        <v>9957376</v>
+        <v>7049900</v>
       </c>
       <c r="C28" s="0">
-        <v>38720505</v>
+        <v>51785547</v>
       </c>
     </row>
     <row r="29">
@@ -607,10 +607,10 @@
         <v>28</v>
       </c>
       <c r="B29" s="0">
-        <v>11810816</v>
+        <v>8362150</v>
       </c>
       <c r="C29" s="0">
-        <v>45619895</v>
+        <v>61773661</v>
       </c>
     </row>
     <row r="30">
@@ -618,10 +618,10 @@
         <v>29</v>
       </c>
       <c r="B30" s="0">
-        <v>14120960</v>
+        <v>9997750</v>
       </c>
       <c r="C30" s="0">
-        <v>54118037</v>
+        <v>73868131</v>
       </c>
     </row>
     <row r="31">
@@ -629,10 +629,10 @@
         <v>30</v>
       </c>
       <c r="B31" s="0">
-        <v>17098752</v>
+        <v>12106050</v>
       </c>
       <c r="C31" s="0">
-        <v>64897339</v>
+        <v>88799165</v>
       </c>
     </row>
     <row r="32">
@@ -640,10 +640,10 @@
         <v>31</v>
       </c>
       <c r="B32" s="0">
-        <v>21108736</v>
+        <v>14945150</v>
       </c>
       <c r="C32" s="0">
-        <v>79153620</v>
+        <v>107804084</v>
       </c>
     </row>
     <row r="33">
@@ -651,10 +651,10 @@
         <v>32</v>
       </c>
       <c r="B33" s="0">
-        <v>26867712</v>
+        <v>19022550</v>
       </c>
       <c r="C33" s="0">
-        <v>99847867</v>
+        <v>133250393</v>
       </c>
     </row>
     <row r="34">
@@ -662,10 +662,10 @@
         <v>33</v>
       </c>
       <c r="B34" s="0">
-        <v>35973120</v>
+        <v>25469250</v>
       </c>
       <c r="C34" s="0">
-        <v>134487696</v>
+        <v>170645503</v>
       </c>
     </row>
     <row r="35">
@@ -673,10 +673,10 @@
         <v>34</v>
       </c>
       <c r="B35" s="0">
-        <v>52862976</v>
+        <v>37427400</v>
       </c>
       <c r="C35" s="0">
-        <v>207137307</v>
+        <v>238701443</v>
       </c>
     </row>
     <row r="36">
@@ -684,10 +684,10 @@
         <v>35</v>
       </c>
       <c r="B36" s="0">
-        <v>96200704</v>
+        <v>68110850</v>
       </c>
       <c r="C36" s="0">
-        <v>652428101</v>
+        <v>580751421</v>
       </c>
     </row>
     <row r="37">
@@ -695,10 +695,10 @@
         <v>36</v>
       </c>
       <c r="B37" s="0">
-        <v>483258368</v>
+        <v>342150700</v>
       </c>
       <c r="C37" s="0">
-        <v>783998773</v>
+        <v>580522433</v>
       </c>
     </row>
     <row r="38">
@@ -706,10 +706,10 @@
         <v>37</v>
       </c>
       <c r="B38" s="0">
-        <v>160835584</v>
+        <v>113872850</v>
       </c>
       <c r="C38" s="0">
-        <v>778488598</v>
+        <v>580522433</v>
       </c>
     </row>
     <row r="39">
@@ -717,10 +717,10 @@
         <v>38</v>
       </c>
       <c r="B39" s="0">
-        <v>68392960</v>
+        <v>48422750</v>
       </c>
       <c r="C39" s="0">
-        <v>792381100</v>
+        <v>580522433</v>
       </c>
     </row>
     <row r="40">
@@ -728,10 +728,10 @@
         <v>39</v>
       </c>
       <c r="B40" s="0">
-        <v>42913792</v>
+        <v>30383300</v>
       </c>
       <c r="C40" s="0">
-        <v>798615978</v>
+        <v>580522433</v>
       </c>
     </row>
     <row r="41">
@@ -739,10 +739,10 @@
         <v>40</v>
       </c>
       <c r="B41" s="0">
-        <v>30836736</v>
+        <v>21832650</v>
       </c>
       <c r="C41" s="0">
-        <v>817196822</v>
+        <v>580522433</v>
       </c>
     </row>
     <row r="42">
@@ -750,10 +750,10 @@
         <v>41</v>
       </c>
       <c r="B42" s="0">
-        <v>23701504</v>
+        <v>16780850</v>
       </c>
       <c r="C42" s="0">
-        <v>833598108</v>
+        <v>580522433</v>
       </c>
     </row>
     <row r="43">
@@ -761,10 +761,10 @@
         <v>42</v>
       </c>
       <c r="B43" s="0">
-        <v>18941952</v>
+        <v>13411050</v>
       </c>
       <c r="C43" s="0">
-        <v>843594468</v>
+        <v>580522433</v>
       </c>
     </row>
     <row r="44">
@@ -772,10 +772,10 @@
         <v>43</v>
       </c>
       <c r="B44" s="0">
-        <v>15509504</v>
+        <v>10980850</v>
       </c>
       <c r="C44" s="0">
-        <v>856492772</v>
+        <v>580522433</v>
       </c>
     </row>
     <row r="45">
@@ -783,10 +783,10 @@
         <v>44</v>
       </c>
       <c r="B45" s="0">
-        <v>12898304</v>
+        <v>9132100</v>
       </c>
       <c r="C45" s="0">
-        <v>849672673</v>
+        <v>580522433</v>
       </c>
     </row>
     <row r="46">
@@ -794,10 +794,10 @@
         <v>45</v>
       </c>
       <c r="B46" s="0">
-        <v>10835968</v>
+        <v>7671950</v>
       </c>
       <c r="C46" s="0">
-        <v>851650181</v>
+        <v>580522433</v>
       </c>
     </row>
     <row r="47">
@@ -805,10 +805,10 @@
         <v>46</v>
       </c>
       <c r="B47" s="0">
-        <v>9162752</v>
+        <v>6487300</v>
       </c>
       <c r="C47" s="0">
-        <v>843875973</v>
+        <v>580522433</v>
       </c>
     </row>
     <row r="48">
@@ -816,10 +816,10 @@
         <v>47</v>
       </c>
       <c r="B48" s="0">
-        <v>7774208</v>
+        <v>5504200</v>
       </c>
       <c r="C48" s="0">
-        <v>845105079</v>
+        <v>580522433</v>
       </c>
     </row>
     <row r="49">
@@ -827,10 +827,10 @@
         <v>48</v>
       </c>
       <c r="B49" s="0">
-        <v>6606848</v>
+        <v>4677700</v>
       </c>
       <c r="C49" s="0">
-        <v>850545207</v>
+        <v>580522433</v>
       </c>
     </row>
     <row r="50">
@@ -838,10 +838,10 @@
         <v>49</v>
       </c>
       <c r="B50" s="0">
-        <v>5615616</v>
+        <v>3975900</v>
       </c>
       <c r="C50" s="0">
-        <v>848874421</v>
+        <v>580522433</v>
       </c>
     </row>
     <row r="51">
@@ -849,10 +849,10 @@
         <v>50</v>
       </c>
       <c r="B51" s="0">
-        <v>4765696</v>
+        <v>3374150</v>
       </c>
       <c r="C51" s="0">
-        <v>852907011</v>
+        <v>580522433</v>
       </c>
     </row>
     <row r="52">
@@ -860,10 +860,10 @@
         <v>51</v>
       </c>
       <c r="B52" s="0">
-        <v>4034560</v>
+        <v>2856500</v>
       </c>
       <c r="C52" s="0">
-        <v>854372895</v>
+        <v>580522433</v>
       </c>
     </row>
     <row r="53">
@@ -871,10 +871,10 @@
         <v>52</v>
       </c>
       <c r="B53" s="0">
-        <v>3403776</v>
+        <v>2409900</v>
       </c>
       <c r="C53" s="0">
-        <v>857230507</v>
+        <v>580522433</v>
       </c>
     </row>
     <row r="54">
@@ -882,10 +882,10 @@
         <v>53</v>
       </c>
       <c r="B54" s="0">
-        <v>2859008</v>
+        <v>2024200</v>
       </c>
       <c r="C54" s="0">
-        <v>854841658</v>
+        <v>580522433</v>
       </c>
     </row>
     <row r="55">
@@ -893,10 +893,10 @@
         <v>54</v>
       </c>
       <c r="B55" s="0">
-        <v>2390016</v>
+        <v>1692150</v>
       </c>
       <c r="C55" s="0">
-        <v>855031582</v>
+        <v>580522433</v>
       </c>
     </row>
     <row r="56">
@@ -904,10 +904,10 @@
         <v>55</v>
       </c>
       <c r="B56" s="0">
-        <v>1984512</v>
+        <v>1405050</v>
       </c>
       <c r="C56" s="0">
-        <v>854252382</v>
+        <v>580522433</v>
       </c>
     </row>
     <row r="57">
@@ -915,10 +915,10 @@
         <v>56</v>
       </c>
       <c r="B57" s="0">
-        <v>1638400</v>
+        <v>1160000</v>
       </c>
       <c r="C57" s="0">
-        <v>855379637</v>
+        <v>580522433</v>
       </c>
     </row>
     <row r="58">
@@ -926,10 +926,10 @@
         <v>57</v>
       </c>
       <c r="B58" s="0">
-        <v>1341440</v>
+        <v>949750</v>
       </c>
       <c r="C58" s="0">
-        <v>854911826</v>
+        <v>580522433</v>
       </c>
     </row>
     <row r="59">
@@ -937,10 +937,10 @@
         <v>58</v>
       </c>
       <c r="B59" s="0">
-        <v>1087488</v>
+        <v>769950</v>
       </c>
       <c r="C59" s="0">
-        <v>854158171</v>
+        <v>580522433</v>
       </c>
     </row>
     <row r="60">
@@ -948,10 +948,10 @@
         <v>59</v>
       </c>
       <c r="B60" s="0">
-        <v>874496</v>
+        <v>619150</v>
       </c>
       <c r="C60" s="0">
-        <v>854852443</v>
+        <v>580522433</v>
       </c>
     </row>
     <row r="61">
@@ -959,10 +959,10 @@
         <v>60</v>
       </c>
       <c r="B61" s="0">
-        <v>694272</v>
+        <v>491550</v>
       </c>
       <c r="C61" s="0">
-        <v>854307675</v>
+        <v>580522433</v>
       </c>
     </row>
     <row r="62">
@@ -970,10 +970,10 @@
         <v>61</v>
       </c>
       <c r="B62" s="0">
-        <v>544768</v>
+        <v>385700</v>
       </c>
       <c r="C62" s="0">
-        <v>854554463</v>
+        <v>580522433</v>
       </c>
     </row>
     <row r="63">
@@ -981,10 +981,10 @@
         <v>62</v>
       </c>
       <c r="B63" s="0">
-        <v>421888</v>
+        <v>298700</v>
       </c>
       <c r="C63" s="0">
-        <v>854261495</v>
+        <v>580522433</v>
       </c>
     </row>
     <row r="64">
@@ -992,10 +992,10 @@
         <v>63</v>
       </c>
       <c r="B64" s="0">
-        <v>319488</v>
+        <v>226200</v>
       </c>
       <c r="C64" s="0">
-        <v>854464727</v>
+        <v>580522433</v>
       </c>
     </row>
     <row r="65">
@@ -1003,10 +1003,10 @@
         <v>64</v>
       </c>
       <c r="B65" s="0">
-        <v>237568</v>
+        <v>168200</v>
       </c>
       <c r="C65" s="0">
-        <v>854292695</v>
+        <v>580522433</v>
       </c>
     </row>
     <row r="66">
@@ -1014,10 +1014,10 @@
         <v>65</v>
       </c>
       <c r="B66" s="0">
-        <v>172032</v>
+        <v>121800</v>
       </c>
       <c r="C66" s="0">
-        <v>854411479</v>
+        <v>580522433</v>
       </c>
     </row>
     <row r="67">
@@ -1025,10 +1025,10 @@
         <v>66</v>
       </c>
       <c r="B67" s="0">
-        <v>118784</v>
+        <v>84100</v>
       </c>
       <c r="C67" s="0">
-        <v>854331607</v>
+        <v>580522433</v>
       </c>
     </row>
     <row r="68">
@@ -1036,10 +1036,10 @@
         <v>67</v>
       </c>
       <c r="B68" s="0">
-        <v>79872</v>
+        <v>56550</v>
       </c>
       <c r="C68" s="0">
-        <v>854341207</v>
+        <v>580522433</v>
       </c>
     </row>
     <row r="69">
@@ -1047,10 +1047,10 @@
         <v>68</v>
       </c>
       <c r="B69" s="0">
-        <v>49152</v>
+        <v>34800</v>
       </c>
       <c r="C69" s="0">
-        <v>854333394</v>
+        <v>580522433</v>
       </c>
     </row>
     <row r="70">
@@ -1058,10 +1058,10 @@
         <v>69</v>
       </c>
       <c r="B70" s="0">
-        <v>26624</v>
+        <v>18850</v>
       </c>
       <c r="C70" s="0">
-        <v>854341206</v>
+        <v>580522433</v>
       </c>
     </row>
     <row r="71">
@@ -1069,10 +1069,10 @@
         <v>70</v>
       </c>
       <c r="B71" s="0">
-        <v>12288</v>
+        <v>8700</v>
       </c>
       <c r="C71" s="0">
-        <v>854340712</v>
+        <v>580522433</v>
       </c>
     </row>
     <row r="72">
@@ -1080,10 +1080,10 @@
         <v>71</v>
       </c>
       <c r="B72" s="0">
-        <v>4096</v>
+        <v>2900</v>
       </c>
       <c r="C72" s="0">
-        <v>854340712</v>
+        <v>580522433</v>
       </c>
     </row>
     <row r="73">
@@ -1094,7 +1094,7 @@
         <v>0</v>
       </c>
       <c r="C73" s="0">
-        <v>854342759</v>
+        <v>580522433</v>
       </c>
     </row>
     <row r="74">
@@ -1102,7 +1102,7 @@
         <v>73</v>
       </c>
       <c r="B74" s="0">
-        <v>2048</v>
+        <v>1450</v>
       </c>
       <c r="C74" s="0">
         <v>0</v>

--- a/src/width_txt/Максимальные_значения_фильтра_дробной_задержки_АЦП_№3.xlsx
+++ b/src/width_txt/Максимальные_значения_фильтра_дробной_задержки_АЦП_№3.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="912" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="4109" uniqueCount="77">
   <si>
     <t>Row</t>
   </si>
@@ -241,6 +241,9 @@
   </si>
   <si>
     <t>Adders_fractional</t>
+  </si>
+  <si>
+    <t>y_fractional_outInt</t>
   </si>
 </sst>
 </file>
@@ -286,12 +289,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C74"/>
+  <dimension ref="A1:D74"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="true"/>
     <col min="2" max="2" width="20.28515625" customWidth="true"/>
     <col min="3" max="3" width="16.85546875" customWidth="true"/>
+    <col min="4" max="4" width="18" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -304,16 +308,22 @@
       <c r="C1" s="0" t="s">
         <v>75</v>
       </c>
+      <c r="D1" s="0" t="s">
+        <v>76</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="0" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="0">
-        <v>1450</v>
+        <v>0</v>
       </c>
       <c r="C2" s="0">
-        <v>7248</v>
+        <v>0</v>
+      </c>
+      <c r="D2" s="0">
+        <v>2157</v>
       </c>
     </row>
     <row r="3">
@@ -321,10 +331,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="0">
-        <v>5800</v>
+        <v>0</v>
       </c>
       <c r="C3" s="0">
-        <v>20290</v>
+        <v>6135</v>
+      </c>
+      <c r="D3" s="0">
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -332,10 +345,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="0">
-        <v>13050</v>
+        <v>6135</v>
       </c>
       <c r="C4" s="0">
-        <v>46372</v>
+        <v>6135</v>
+      </c>
+      <c r="D4" s="0">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -343,10 +359,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="0">
-        <v>26100</v>
+        <v>0</v>
       </c>
       <c r="C5" s="0">
-        <v>91286</v>
+        <v>23616</v>
+      </c>
+      <c r="D5" s="0">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -354,10 +373,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="0">
-        <v>44950</v>
+        <v>18405</v>
       </c>
       <c r="C6" s="0">
-        <v>160835</v>
+        <v>23043</v>
+      </c>
+      <c r="D6" s="0">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -365,10 +387,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="0">
-        <v>69600</v>
+        <v>6135</v>
       </c>
       <c r="C7" s="0">
-        <v>262259</v>
+        <v>49995</v>
+      </c>
+      <c r="D7" s="0">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -376,10 +401,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="0">
-        <v>101500</v>
+        <v>36810</v>
       </c>
       <c r="C8" s="0">
-        <v>405698</v>
+        <v>46512</v>
+      </c>
+      <c r="D8" s="0">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -387,10 +415,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="0">
-        <v>143550</v>
+        <v>14315</v>
       </c>
       <c r="C9" s="0">
-        <v>601294</v>
+        <v>69325</v>
+      </c>
+      <c r="D9" s="0">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -398,10 +429,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="0">
-        <v>195750</v>
+        <v>42945</v>
       </c>
       <c r="C10" s="0">
-        <v>862084</v>
+        <v>61339</v>
+      </c>
+      <c r="D10" s="0">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -409,10 +443,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="0">
-        <v>261000</v>
+        <v>12270</v>
       </c>
       <c r="C11" s="0">
-        <v>1201106</v>
+        <v>64479</v>
+      </c>
+      <c r="D11" s="0">
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -420,10 +457,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="0">
-        <v>339300</v>
+        <v>8180</v>
       </c>
       <c r="C12" s="0">
-        <v>1637191</v>
+        <v>65664</v>
+      </c>
+      <c r="D12" s="0">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -431,10 +471,13 @@
         <v>12</v>
       </c>
       <c r="B13" s="0">
-        <v>436450</v>
+        <v>12270</v>
       </c>
       <c r="C13" s="0">
-        <v>2189171</v>
+        <v>119706</v>
+      </c>
+      <c r="D13" s="0">
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -442,10 +485,13 @@
         <v>13</v>
       </c>
       <c r="B14" s="0">
-        <v>552450</v>
+        <v>96115</v>
       </c>
       <c r="C14" s="0">
-        <v>2880222</v>
+        <v>114360</v>
+      </c>
+      <c r="D14" s="0">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -453,10 +499,13 @@
         <v>14</v>
       </c>
       <c r="B15" s="0">
-        <v>691650</v>
+        <v>63395</v>
       </c>
       <c r="C15" s="0">
-        <v>3734972</v>
+        <v>343082</v>
+      </c>
+      <c r="D15" s="0">
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -464,10 +513,13 @@
         <v>15</v>
       </c>
       <c r="B16" s="0">
-        <v>855500</v>
+        <v>282210</v>
       </c>
       <c r="C16" s="0">
-        <v>4783837</v>
+        <v>342557</v>
+      </c>
+      <c r="D16" s="0">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -475,10 +527,13 @@
         <v>16</v>
       </c>
       <c r="B17" s="0">
-        <v>1049800</v>
+        <v>108385</v>
       </c>
       <c r="C17" s="0">
-        <v>6060136</v>
+        <v>729911</v>
+      </c>
+      <c r="D17" s="0">
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -486,10 +541,13 @@
         <v>17</v>
       </c>
       <c r="B18" s="0">
-        <v>1277450</v>
+        <v>529655</v>
       </c>
       <c r="C18" s="0">
-        <v>7601526</v>
+        <v>697937</v>
+      </c>
+      <c r="D18" s="0">
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -497,10 +555,13 @@
         <v>18</v>
       </c>
       <c r="B19" s="0">
-        <v>1542800</v>
+        <v>73620</v>
       </c>
       <c r="C19" s="0">
-        <v>9451468</v>
+        <v>1273582</v>
+      </c>
+      <c r="D19" s="0">
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -508,10 +569,13 @@
         <v>19</v>
       </c>
       <c r="B20" s="0">
-        <v>1851650</v>
+        <v>756650</v>
       </c>
       <c r="C20" s="0">
-        <v>11659207</v>
+        <v>1389947</v>
+      </c>
+      <c r="D20" s="0">
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -519,10 +583,13 @@
         <v>20</v>
       </c>
       <c r="B21" s="0">
-        <v>2209800</v>
+        <v>149285</v>
       </c>
       <c r="C21" s="0">
-        <v>14281237</v>
+        <v>2009323</v>
+      </c>
+      <c r="D21" s="0">
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -530,10 +597,13 @@
         <v>21</v>
       </c>
       <c r="B22" s="0">
-        <v>2624500</v>
+        <v>860945</v>
       </c>
       <c r="C22" s="0">
-        <v>17384190</v>
+        <v>2449884</v>
+      </c>
+      <c r="D22" s="0">
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -541,10 +611,13 @@
         <v>22</v>
       </c>
       <c r="B23" s="0">
-        <v>3105900</v>
+        <v>676895</v>
       </c>
       <c r="C23" s="0">
-        <v>21043391</v>
+        <v>2933940</v>
+      </c>
+      <c r="D23" s="0">
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -552,10 +625,13 @@
         <v>23</v>
       </c>
       <c r="B24" s="0">
-        <v>3662700</v>
+        <v>744380</v>
       </c>
       <c r="C24" s="0">
-        <v>25351546</v>
+        <v>3859013</v>
+      </c>
+      <c r="D24" s="0">
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -563,10 +639,13 @@
         <v>24</v>
       </c>
       <c r="B25" s="0">
-        <v>4312300</v>
+        <v>1556245</v>
       </c>
       <c r="C25" s="0">
-        <v>30420198</v>
+        <v>4063370</v>
+      </c>
+      <c r="D25" s="0">
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -574,10 +653,13 @@
         <v>25</v>
       </c>
       <c r="B26" s="0">
-        <v>5073550</v>
+        <v>390595</v>
       </c>
       <c r="C26" s="0">
-        <v>36388416</v>
+        <v>5481056</v>
+      </c>
+      <c r="D26" s="0">
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -585,10 +667,13 @@
         <v>26</v>
       </c>
       <c r="B27" s="0">
-        <v>5974000</v>
+        <v>2705535</v>
       </c>
       <c r="C27" s="0">
-        <v>43431489</v>
+        <v>5448170</v>
+      </c>
+      <c r="D27" s="0">
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -596,10 +681,13 @@
         <v>27</v>
       </c>
       <c r="B28" s="0">
-        <v>7049900</v>
+        <v>85890</v>
       </c>
       <c r="C28" s="0">
-        <v>51785547</v>
+        <v>7098829</v>
+      </c>
+      <c r="D28" s="0">
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -607,10 +695,13 @@
         <v>28</v>
       </c>
       <c r="B29" s="0">
-        <v>8362150</v>
+        <v>3879365</v>
       </c>
       <c r="C29" s="0">
-        <v>61773661</v>
+        <v>6943012</v>
+      </c>
+      <c r="D29" s="0">
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -618,10 +709,13 @@
         <v>29</v>
       </c>
       <c r="B30" s="0">
-        <v>9997750</v>
+        <v>406955</v>
       </c>
       <c r="C30" s="0">
-        <v>73868131</v>
+        <v>8408212</v>
+      </c>
+      <c r="D30" s="0">
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -629,10 +723,13 @@
         <v>30</v>
       </c>
       <c r="B31" s="0">
-        <v>12106050</v>
+        <v>4644195</v>
       </c>
       <c r="C31" s="0">
-        <v>88799165</v>
+        <v>8364308</v>
+      </c>
+      <c r="D31" s="0">
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -640,10 +737,13 @@
         <v>31</v>
       </c>
       <c r="B32" s="0">
-        <v>14945150</v>
+        <v>114520</v>
       </c>
       <c r="C32" s="0">
-        <v>107804084</v>
+        <v>9320098</v>
+      </c>
+      <c r="D32" s="0">
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -651,10 +751,13 @@
         <v>32</v>
       </c>
       <c r="B33" s="0">
-        <v>19022550</v>
+        <v>4331310</v>
       </c>
       <c r="C33" s="0">
-        <v>133250393</v>
+        <v>9660774</v>
+      </c>
+      <c r="D33" s="0">
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -662,10 +765,13 @@
         <v>33</v>
       </c>
       <c r="B34" s="0">
-        <v>25469250</v>
+        <v>1676900</v>
       </c>
       <c r="C34" s="0">
-        <v>170645503</v>
+        <v>9755974</v>
+      </c>
+      <c r="D34" s="0">
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -673,10 +779,13 @@
         <v>34</v>
       </c>
       <c r="B35" s="0">
-        <v>37427400</v>
+        <v>1216775</v>
       </c>
       <c r="C35" s="0">
-        <v>238701443</v>
+        <v>12397292</v>
+      </c>
+      <c r="D35" s="0">
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -684,10 +793,13 @@
         <v>35</v>
       </c>
       <c r="B36" s="0">
-        <v>68110850</v>
+        <v>9764875</v>
       </c>
       <c r="C36" s="0">
-        <v>580751421</v>
+        <v>50019494</v>
+      </c>
+      <c r="D36" s="0">
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -695,10 +807,13 @@
         <v>36</v>
       </c>
       <c r="B37" s="0">
-        <v>342150700</v>
+        <v>53229305</v>
       </c>
       <c r="C37" s="0">
-        <v>580522433</v>
+        <v>70684405</v>
+      </c>
+      <c r="D37" s="0">
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -706,10 +821,13 @@
         <v>37</v>
       </c>
       <c r="B38" s="0">
-        <v>113872850</v>
+        <v>21178020</v>
       </c>
       <c r="C38" s="0">
-        <v>580522433</v>
+        <v>70667257</v>
+      </c>
+      <c r="D38" s="0">
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -717,10 +835,13 @@
         <v>38</v>
       </c>
       <c r="B39" s="0">
-        <v>48422750</v>
+        <v>14200480</v>
       </c>
       <c r="C39" s="0">
-        <v>580522433</v>
+        <v>70667257</v>
+      </c>
+      <c r="D39" s="0">
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -728,10 +849,13 @@
         <v>39</v>
       </c>
       <c r="B40" s="0">
-        <v>30383300</v>
+        <v>5008205</v>
       </c>
       <c r="C40" s="0">
-        <v>580522433</v>
+        <v>70667257</v>
+      </c>
+      <c r="D40" s="0">
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -739,10 +863,13 @@
         <v>40</v>
       </c>
       <c r="B41" s="0">
-        <v>21832650</v>
+        <v>7709650</v>
       </c>
       <c r="C41" s="0">
-        <v>580522433</v>
+        <v>70667257</v>
+      </c>
+      <c r="D41" s="0">
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -750,10 +877,13 @@
         <v>41</v>
       </c>
       <c r="B42" s="0">
-        <v>16780850</v>
+        <v>1198370</v>
       </c>
       <c r="C42" s="0">
-        <v>580522433</v>
+        <v>70667257</v>
+      </c>
+      <c r="D42" s="0">
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -761,10 +891,13 @@
         <v>42</v>
       </c>
       <c r="B43" s="0">
-        <v>13411050</v>
+        <v>4441740</v>
       </c>
       <c r="C43" s="0">
-        <v>580522433</v>
+        <v>70667257</v>
+      </c>
+      <c r="D43" s="0">
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -772,10 +905,13 @@
         <v>43</v>
       </c>
       <c r="B44" s="0">
-        <v>10980850</v>
+        <v>869125</v>
       </c>
       <c r="C44" s="0">
-        <v>580522433</v>
+        <v>70667257</v>
+      </c>
+      <c r="D44" s="0">
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -783,10 +919,13 @@
         <v>44</v>
       </c>
       <c r="B45" s="0">
-        <v>9132100</v>
+        <v>2257680</v>
       </c>
       <c r="C45" s="0">
-        <v>580522433</v>
+        <v>70667257</v>
+      </c>
+      <c r="D45" s="0">
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -794,10 +933,13 @@
         <v>45</v>
       </c>
       <c r="B46" s="0">
-        <v>7671950</v>
+        <v>1928435</v>
       </c>
       <c r="C46" s="0">
-        <v>580522433</v>
+        <v>70667257</v>
+      </c>
+      <c r="D46" s="0">
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -805,10 +947,13 @@
         <v>46</v>
       </c>
       <c r="B47" s="0">
-        <v>6487300</v>
+        <v>891620</v>
       </c>
       <c r="C47" s="0">
-        <v>580522433</v>
+        <v>70667257</v>
+      </c>
+      <c r="D47" s="0">
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -816,10 +961,13 @@
         <v>47</v>
       </c>
       <c r="B48" s="0">
-        <v>5504200</v>
+        <v>2206555</v>
       </c>
       <c r="C48" s="0">
-        <v>580522433</v>
+        <v>70667257</v>
+      </c>
+      <c r="D48" s="0">
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -827,10 +975,13 @@
         <v>48</v>
       </c>
       <c r="B49" s="0">
-        <v>4677700</v>
+        <v>202455</v>
       </c>
       <c r="C49" s="0">
-        <v>580522433</v>
+        <v>70667257</v>
+      </c>
+      <c r="D49" s="0">
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -838,10 +989,13 @@
         <v>49</v>
       </c>
       <c r="B50" s="0">
-        <v>3975900</v>
+        <v>1930480</v>
       </c>
       <c r="C50" s="0">
-        <v>580522433</v>
+        <v>70667257</v>
+      </c>
+      <c r="D50" s="0">
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -849,10 +1003,13 @@
         <v>50</v>
       </c>
       <c r="B51" s="0">
-        <v>3374150</v>
+        <v>10225</v>
       </c>
       <c r="C51" s="0">
-        <v>580522433</v>
+        <v>70667257</v>
+      </c>
+      <c r="D51" s="0">
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -860,10 +1017,13 @@
         <v>51</v>
       </c>
       <c r="B52" s="0">
-        <v>2856500</v>
+        <v>1374240</v>
       </c>
       <c r="C52" s="0">
-        <v>580522433</v>
+        <v>70667257</v>
+      </c>
+      <c r="D52" s="0">
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -871,10 +1031,13 @@
         <v>52</v>
       </c>
       <c r="B53" s="0">
-        <v>2409900</v>
+        <v>32720</v>
       </c>
       <c r="C53" s="0">
-        <v>580522433</v>
+        <v>70667257</v>
+      </c>
+      <c r="D53" s="0">
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -882,10 +1045,13 @@
         <v>53</v>
       </c>
       <c r="B54" s="0">
-        <v>2024200</v>
+        <v>783235</v>
       </c>
       <c r="C54" s="0">
-        <v>580522433</v>
+        <v>70667257</v>
+      </c>
+      <c r="D54" s="0">
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -893,10 +1059,13 @@
         <v>54</v>
       </c>
       <c r="B55" s="0">
-        <v>1692150</v>
+        <v>139060</v>
       </c>
       <c r="C55" s="0">
-        <v>580522433</v>
+        <v>70667257</v>
+      </c>
+      <c r="D55" s="0">
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -904,10 +1073,13 @@
         <v>55</v>
       </c>
       <c r="B56" s="0">
-        <v>1405050</v>
+        <v>316975</v>
       </c>
       <c r="C56" s="0">
-        <v>580522433</v>
+        <v>70667257</v>
+      </c>
+      <c r="D56" s="0">
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -915,10 +1087,13 @@
         <v>56</v>
       </c>
       <c r="B57" s="0">
-        <v>1160000</v>
+        <v>202455</v>
       </c>
       <c r="C57" s="0">
-        <v>580522433</v>
+        <v>70667257</v>
+      </c>
+      <c r="D57" s="0">
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -926,10 +1101,13 @@
         <v>57</v>
       </c>
       <c r="B58" s="0">
-        <v>949750</v>
+        <v>34765</v>
       </c>
       <c r="C58" s="0">
-        <v>580522433</v>
+        <v>70667257</v>
+      </c>
+      <c r="D58" s="0">
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -937,10 +1115,13 @@
         <v>58</v>
       </c>
       <c r="B59" s="0">
-        <v>769950</v>
+        <v>192230</v>
       </c>
       <c r="C59" s="0">
-        <v>580522433</v>
+        <v>70667257</v>
+      </c>
+      <c r="D59" s="0">
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -948,10 +1129,13 @@
         <v>59</v>
       </c>
       <c r="B60" s="0">
-        <v>619150</v>
+        <v>81800</v>
       </c>
       <c r="C60" s="0">
-        <v>580522433</v>
+        <v>70667257</v>
+      </c>
+      <c r="D60" s="0">
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -959,10 +1143,13 @@
         <v>60</v>
       </c>
       <c r="B61" s="0">
-        <v>491550</v>
+        <v>134970</v>
       </c>
       <c r="C61" s="0">
-        <v>580522433</v>
+        <v>70667257</v>
+      </c>
+      <c r="D61" s="0">
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -970,10 +1157,13 @@
         <v>61</v>
       </c>
       <c r="B62" s="0">
-        <v>385700</v>
+        <v>92025</v>
       </c>
       <c r="C62" s="0">
-        <v>580522433</v>
+        <v>70667257</v>
+      </c>
+      <c r="D62" s="0">
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -981,10 +1171,13 @@
         <v>62</v>
       </c>
       <c r="B63" s="0">
-        <v>298700</v>
+        <v>65440</v>
       </c>
       <c r="C63" s="0">
-        <v>580522433</v>
+        <v>70667257</v>
+      </c>
+      <c r="D63" s="0">
+        <v>0</v>
       </c>
     </row>
     <row r="64">
@@ -992,10 +1185,13 @@
         <v>63</v>
       </c>
       <c r="B64" s="0">
-        <v>226200</v>
+        <v>61350</v>
       </c>
       <c r="C64" s="0">
-        <v>580522433</v>
+        <v>70667257</v>
+      </c>
+      <c r="D64" s="0">
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -1003,10 +1199,13 @@
         <v>64</v>
       </c>
       <c r="B65" s="0">
-        <v>168200</v>
+        <v>16360</v>
       </c>
       <c r="C65" s="0">
-        <v>580522433</v>
+        <v>70667257</v>
+      </c>
+      <c r="D65" s="0">
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -1014,10 +1213,13 @@
         <v>65</v>
       </c>
       <c r="B66" s="0">
-        <v>121800</v>
+        <v>28630</v>
       </c>
       <c r="C66" s="0">
-        <v>580522433</v>
+        <v>70667257</v>
+      </c>
+      <c r="D66" s="0">
+        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -1025,10 +1227,13 @@
         <v>66</v>
       </c>
       <c r="B67" s="0">
-        <v>84100</v>
+        <v>6135</v>
       </c>
       <c r="C67" s="0">
-        <v>580522433</v>
+        <v>70667257</v>
+      </c>
+      <c r="D67" s="0">
+        <v>0</v>
       </c>
     </row>
     <row r="68">
@@ -1036,10 +1241,13 @@
         <v>67</v>
       </c>
       <c r="B68" s="0">
-        <v>56550</v>
+        <v>8180</v>
       </c>
       <c r="C68" s="0">
-        <v>580522433</v>
+        <v>70667257</v>
+      </c>
+      <c r="D68" s="0">
+        <v>0</v>
       </c>
     </row>
     <row r="69">
@@ -1047,10 +1255,13 @@
         <v>68</v>
       </c>
       <c r="B69" s="0">
-        <v>34800</v>
+        <v>10225</v>
       </c>
       <c r="C69" s="0">
-        <v>580522433</v>
+        <v>70667257</v>
+      </c>
+      <c r="D69" s="0">
+        <v>0</v>
       </c>
     </row>
     <row r="70">
@@ -1058,10 +1269,13 @@
         <v>69</v>
       </c>
       <c r="B70" s="0">
-        <v>18850</v>
+        <v>2045</v>
       </c>
       <c r="C70" s="0">
-        <v>580522433</v>
+        <v>70667257</v>
+      </c>
+      <c r="D70" s="0">
+        <v>0</v>
       </c>
     </row>
     <row r="71">
@@ -1069,10 +1283,13 @@
         <v>70</v>
       </c>
       <c r="B71" s="0">
-        <v>8700</v>
+        <v>4090</v>
       </c>
       <c r="C71" s="0">
-        <v>580522433</v>
+        <v>70667257</v>
+      </c>
+      <c r="D71" s="0">
+        <v>0</v>
       </c>
     </row>
     <row r="72">
@@ -1080,10 +1297,13 @@
         <v>71</v>
       </c>
       <c r="B72" s="0">
-        <v>2900</v>
+        <v>0</v>
       </c>
       <c r="C72" s="0">
-        <v>580522433</v>
+        <v>70667257</v>
+      </c>
+      <c r="D72" s="0">
+        <v>0</v>
       </c>
     </row>
     <row r="73">
@@ -1094,7 +1314,10 @@
         <v>0</v>
       </c>
       <c r="C73" s="0">
-        <v>580522433</v>
+        <v>70667257</v>
+      </c>
+      <c r="D73" s="0">
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -1102,9 +1325,12 @@
         <v>73</v>
       </c>
       <c r="B74" s="0">
-        <v>1450</v>
+        <v>0</v>
       </c>
       <c r="C74" s="0">
+        <v>0</v>
+      </c>
+      <c r="D74" s="0">
         <v>0</v>
       </c>
     </row>
